--- a/excel_files/11.b.2.xlsx
+++ b/excel_files/11.b.2.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Глобальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Глобальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12135"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
@@ -68,9 +68,6 @@
     <t>11.b.2 Proportion of local governments that adopt and implement local disaster risk reduction strategies in line with national disaster risk reduction strategies</t>
   </si>
   <si>
-    <t>1.5.4 Кырсыктардын кооптуулугун азайтуунун улуттук стратегияларына ылайык, кырсыктардын кооптуулугун азайтуунун жергиликтүү стратегияларын кабыл алган жана ишке ашырган жергиликтүү бийлик органдарынын үлүшү</t>
-  </si>
-  <si>
     <t>Жергиликтүү бийлик органдарынын саны</t>
   </si>
   <si>
@@ -78,6 +75,9 @@
   </si>
   <si>
     <t>Улуттук стратегияларга ылайык, кырсыктардын кооптуулугун азайтуу боюнча жергиликтүү DRR стратегияларын кабыл алган жана ишке ашырган жергиликтүү бийлик органдарынын саны</t>
+  </si>
+  <si>
+    <t>11.b.2  Кырсыктардын кооптуулугун азайтуунун улуттук стратегияларына ылайык, кырсыктардын кооптуулугун азайтуунун жергиликтүү стратегияларын кабыл алган жана ишке ашырган жергиликтүү бийлик органдарынын үлүшү</t>
   </si>
 </sst>
 </file>
@@ -8120,15 +8120,15 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:I6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="40.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="79.5" customHeight="1">
+    <row r="1" spans="1:9" ht="79.5" customHeight="1">
       <c r="A1" s="6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>9</v>
@@ -8137,11 +8137,11 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+    <row r="2" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A2" s="1"/>
       <c r="B2" s="7"/>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1">
+    <row r="3" spans="1:9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -8166,10 +8166,13 @@
       <c r="H3" s="4">
         <v>2023</v>
       </c>
+      <c r="I3" s="4">
+        <v>2024</v>
+      </c>
     </row>
-    <row r="4" spans="1:8" ht="21" customHeight="1">
+    <row r="4" spans="1:9" ht="21" customHeight="1">
       <c r="A4" s="14" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="13" t="s">
         <v>3</v>
@@ -8192,10 +8195,13 @@
       <c r="H4" s="16">
         <v>484</v>
       </c>
+      <c r="I4" s="16">
+        <v>484</v>
+      </c>
     </row>
-    <row r="5" spans="1:8" ht="46.5" customHeight="1">
+    <row r="5" spans="1:9" ht="46.5" customHeight="1">
       <c r="A5" s="18" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="8" t="s">
         <v>4</v>
@@ -8218,10 +8224,13 @@
       <c r="H5" s="17">
         <v>40.53</v>
       </c>
+      <c r="I5" s="17">
+        <v>35.5</v>
+      </c>
     </row>
-    <row r="6" spans="1:8" ht="55.5" customHeight="1" thickBot="1">
+    <row r="6" spans="1:9" ht="55.5" customHeight="1" thickBot="1">
       <c r="A6" s="19" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>5</v>
@@ -8244,6 +8253,9 @@
       <c r="H6" s="12">
         <v>169</v>
       </c>
+      <c r="I6" s="12">
+        <v>172</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
